--- a/DesignData/Excel_Masters/WeaponStats_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="159">
   <si>
     <t>CritRate</t>
   </si>
@@ -31,9 +28,6 @@
     <t>CritDamage</t>
   </si>
   <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
     <t>DisplayName</t>
   </si>
   <si>
@@ -44,18 +38,6 @@
   </si>
   <si>
     <t>SetID</t>
-  </si>
-  <si>
-    <t>AttackPower</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelUpCostId</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Uncommon</t>
@@ -81,20 +63,445 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>철검</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검이다</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Iron_Sword</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AttackRange</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Blunt_Cleaner</t>
+  </si>
+  <si>
+    <t>Blunt_DevilBat</t>
+  </si>
+  <si>
+    <t>Blunt_Event_01</t>
+  </si>
+  <si>
+    <t>Blunt_TreasureChest</t>
+  </si>
+  <si>
+    <t>Blunt_Wrench</t>
+  </si>
+  <si>
+    <t>Blunt_DefaultBlunt</t>
+  </si>
+  <si>
+    <t>Blunt_Nobel</t>
+  </si>
+  <si>
+    <t>Blunt_Nurse</t>
+  </si>
+  <si>
+    <t>Blunt_Outsider</t>
+  </si>
+  <si>
+    <t>Blunt_Tuner</t>
+  </si>
+  <si>
+    <t>Book_BookOfRed</t>
+  </si>
+  <si>
+    <t>Book_CookingForDummies</t>
+  </si>
+  <si>
+    <t>Book_DeckCase</t>
+  </si>
+  <si>
+    <t>Book_DefaultBook</t>
+  </si>
+  <si>
+    <t>Book_Dictionary</t>
+  </si>
+  <si>
+    <t>Book_Event_01</t>
+  </si>
+  <si>
+    <t>Book_FlawlessPlaying</t>
+  </si>
+  <si>
+    <t>Book_HologramHud</t>
+  </si>
+  <si>
+    <t>Book_MementoMori</t>
+  </si>
+  <si>
+    <t>Book_PerfectHarmony</t>
+  </si>
+  <si>
+    <t>Gun_PayBack</t>
+  </si>
+  <si>
+    <t>Gun_BlackBeard</t>
+  </si>
+  <si>
+    <t>Gun_LovelyCoil</t>
+  </si>
+  <si>
+    <t>Gun_Mustang</t>
+  </si>
+  <si>
+    <t>Gun_Demonia</t>
+  </si>
+  <si>
+    <t>Gun_Event_01</t>
+  </si>
+  <si>
+    <t>Gun_Nail_Gun</t>
+  </si>
+  <si>
+    <t>Staff_DeathMatch</t>
+  </si>
+  <si>
+    <t>Staff_OneStroke</t>
+  </si>
+  <si>
+    <t>Staff_Decanter</t>
+  </si>
+  <si>
+    <t>Staff_WinterCane</t>
+  </si>
+  <si>
+    <t>Staff_Bard</t>
+  </si>
+  <si>
+    <t>Staff_Event_01</t>
+  </si>
+  <si>
+    <t>Staff_Merry</t>
+  </si>
+  <si>
+    <t>Staff_Rogue</t>
+  </si>
+  <si>
+    <t>Sword_Carver</t>
+  </si>
+  <si>
+    <t>Sword_Army</t>
+  </si>
+  <si>
+    <t>Sword_BeamSword</t>
+  </si>
+  <si>
+    <t>Sword_ButterSlayer</t>
+  </si>
+  <si>
+    <t>Sword_ChainSword</t>
+  </si>
+  <si>
+    <t>Sword_Event_01</t>
+  </si>
+  <si>
+    <t>Sword_Maid</t>
+  </si>
+  <si>
+    <t>Sword_MilkyWay</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>LevelUpCostId</t>
+  </si>
+  <si>
+    <t>AttackPower</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>기본 둔기</t>
+  </si>
+  <si>
+    <t>흔하게 볼 수 있는 나무 몽둥이입니다.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Cost_Normal</t>
+  </si>
+  <si>
+    <t>렌치</t>
+  </si>
+  <si>
+    <t>공구함에서 꺼낸 묵직한 렌치입니다.</t>
+  </si>
+  <si>
+    <t>청소부의 빗자루</t>
+  </si>
+  <si>
+    <t>먼지 대신 적을 쓸어버리는 빗자루입니다.</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Cost_Rare</t>
+  </si>
+  <si>
+    <t>노벨의 망치</t>
+  </si>
+  <si>
+    <t>화약 냄새가 나는 위험한 망치입니다.</t>
+  </si>
+  <si>
+    <t>간호사의 주사기</t>
+  </si>
+  <si>
+    <t>거대한 주사기 형태의 둔기입니다.</t>
+  </si>
+  <si>
+    <t>조율자의 해머</t>
+  </si>
+  <si>
+    <t>불협화음을 부수는 거대한 해머입니다.</t>
+  </si>
+  <si>
+    <t>악마의 방망이</t>
+  </si>
+  <si>
+    <t>악마의 기운이 깃든 가시 박힌 배트입니다.</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Cost_Epic</t>
+  </si>
+  <si>
+    <t>이방인의 곤봉</t>
+  </si>
+  <si>
+    <t>알 수 없는 재질로 만들어진 무거운 곤봉입니다.</t>
+  </si>
+  <si>
+    <t>황금 뿅망치 (이벤트)</t>
+  </si>
+  <si>
+    <t>맞으면 기분이 묘하게 나쁜 뿅망치입니다.</t>
+  </si>
+  <si>
+    <t>보물상자 철퇴</t>
+  </si>
+  <si>
+    <t>금화가 쏟아져 나오는 전설의 철퇴입니다.</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Cost_Legend</t>
+  </si>
+  <si>
+    <t>기본 마도서</t>
+  </si>
+  <si>
+    <t>마법의 기초가 적혀있는 낡은 책입니다.</t>
+  </si>
+  <si>
+    <t>요리 기초 책</t>
+  </si>
+  <si>
+    <t>불 마법을 쓰기 좋은 레시피북입니다.</t>
+  </si>
+  <si>
+    <t>두꺼운 사전</t>
+  </si>
+  <si>
+    <t>물리적으로 때려도 아플 것 같은 사전입니다.</t>
+  </si>
+  <si>
+    <t>덱 케이스</t>
+  </si>
+  <si>
+    <t>마법 카드가 가득 들어있는 케이스입니다.</t>
+  </si>
+  <si>
+    <t>홀로그램 HUD</t>
+  </si>
+  <si>
+    <t>첨단 기술이 집약된 정보 투영기입니다.</t>
+  </si>
+  <si>
+    <t>완벽한 조화</t>
+  </si>
+  <si>
+    <t>자연의 이치가 담긴 신비한 책입니다.</t>
+  </si>
+  <si>
+    <t>붉은 책</t>
+  </si>
+  <si>
+    <t>펼치는 순간 피바람이 부는 마도서입니다.</t>
+  </si>
+  <si>
+    <t>메멘토 모리</t>
+  </si>
+  <si>
+    <t>죽음을 기억하게 만드는 불길한 서적입니다.</t>
+  </si>
+  <si>
+    <t>축제의 마도서 (이벤트)</t>
+  </si>
+  <si>
+    <t>폭죽 마법이 무한히 나옵니다.</t>
+  </si>
+  <si>
+    <t>완벽한 연주보</t>
+  </si>
+  <si>
+    <t>세계를 연주할 수 있는 절대적인 악보입니다.</t>
+  </si>
+  <si>
+    <t>경비병의 총</t>
+  </si>
+  <si>
+    <t>평범한 경비병들이 사용하는 총입니다.</t>
+  </si>
+  <si>
+    <t>네일 건</t>
+  </si>
+  <si>
+    <t>공사장에서 쓰던 못 박는 기계입니다.</t>
+  </si>
+  <si>
+    <t>러블리 코일</t>
+  </si>
+  <si>
+    <t>귀여운 외형과 달리 살상력이 높습니다.</t>
+  </si>
+  <si>
+    <t>머스탱</t>
+  </si>
+  <si>
+    <t>반동이 크지만 위력적인 권총입니다.</t>
+  </si>
+  <si>
+    <t>페이백</t>
+  </si>
+  <si>
+    <t>받은 만큼 돌려주는 쌍권총입니다.</t>
+  </si>
+  <si>
+    <t>데모니아</t>
+  </si>
+  <si>
+    <t>마계의 금속으로 벼려낸 산탄총입니다.</t>
+  </si>
+  <si>
+    <t>물총 (이벤트)</t>
+  </si>
+  <si>
+    <t>생각보다 수압이 강한 장난감 물총입니다.</t>
+  </si>
+  <si>
+    <t>검은 수염의 머스킷</t>
+  </si>
+  <si>
+    <t>해적왕이 애용하던 전설의 흑색 화약총입니다.</t>
+  </si>
+  <si>
+    <t>불량배의 막대기</t>
+  </si>
+  <si>
+    <t>길거리에서 흔히 줍는 긴 막대기입니다.</t>
+  </si>
+  <si>
+    <t>음유시인의 지팡이</t>
+  </si>
+  <si>
+    <t>바람 소리가 나는 가벼운 지팡이입니다.</t>
+  </si>
+  <si>
+    <t>일필휘지</t>
+  </si>
+  <si>
+    <t>허공에 먹물을 흩뿌리는 거대한 붓입니다.</t>
+  </si>
+  <si>
+    <t>디캔터 지팡이</t>
+  </si>
+  <si>
+    <t>포도주가 끊임없이 흐르는 지팡이입니다.</t>
+  </si>
+  <si>
+    <t>메리 스태프</t>
+  </si>
+  <si>
+    <t>즐거운 기운을 뿜어내는 응원용 지팡이입니다.</t>
+  </si>
+  <si>
+    <t>데스매치</t>
+  </si>
+  <si>
+    <t>피를 머금은 전투용 마법 지팡이입니다.</t>
+  </si>
+  <si>
+    <t>겨울의 지팡이</t>
+  </si>
+  <si>
+    <t>주변을 얼어붙게 만드는 혹한의 지팡이입니다.</t>
+  </si>
+  <si>
+    <t>폭죽 지팡이 (이벤트)</t>
+  </si>
+  <si>
+    <t>사용할 때마다 시끄러운 소리가 납니다.</t>
+  </si>
+  <si>
+    <t>보급형 군용검</t>
+  </si>
+  <si>
+    <t>군대에서 대량 생산되는 표준 검입니다.</t>
+  </si>
+  <si>
+    <t>버터 슬레이어</t>
+  </si>
+  <si>
+    <t>버터처럼 적을 부드럽게 베어냅니다.</t>
+  </si>
+  <si>
+    <t>조각가의 검</t>
+  </si>
+  <si>
+    <t>정밀한 타격이 가능한 예리한 소검입니다.</t>
+  </si>
+  <si>
+    <t>메이드의 장검</t>
+  </si>
+  <si>
+    <t>청소와 암살에 모두 능한 메이드의 검입니다.</t>
+  </si>
+  <si>
+    <t>빔 소드</t>
+  </si>
+  <si>
+    <t>고열의 플라즈마로 이루어진 검입니다.</t>
+  </si>
+  <si>
+    <t>체인 소드</t>
+  </si>
+  <si>
+    <t>톱니바퀴가 돌아가며 살점을 찢어냅니다.</t>
+  </si>
+  <si>
+    <t>광선검 (이벤트)</t>
+  </si>
+  <si>
+    <t>웅웅거리는 소리가 매력적인 장난감입니다.</t>
+  </si>
+  <si>
+    <t>은하수 검</t>
+  </si>
+  <si>
+    <t>휘두를 때마다 별빛이 쏟아지는 성검입니다.</t>
+  </si>
+  <si>
+    <t>Gun_Smithers</t>
+  </si>
+  <si>
+    <t>Gun_BlackNose</t>
+  </si>
+  <si>
+    <t>블랙 노즈</t>
+  </si>
+  <si>
+    <t>화약 냄새가 짙게 밴 검은 총열의 권총입니다.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +1094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -697,6 +1104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1018,30 +1426,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1053,76 +1461,1478 @@
         <v>5</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>55</v>
+      </c>
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="D2">
+        <v>0.05</v>
+      </c>
+      <c r="E2">
+        <v>1.5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>60</v>
+      </c>
+      <c r="C3">
+        <v>0.85</v>
+      </c>
+      <c r="D3">
+        <v>0.05</v>
+      </c>
+      <c r="E3">
+        <v>1.6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>75</v>
+      </c>
+      <c r="C4">
+        <v>0.9</v>
+      </c>
+      <c r="D4">
+        <v>0.05</v>
+      </c>
+      <c r="E4">
+        <v>1.8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>0.75</v>
+      </c>
+      <c r="D5">
+        <v>0.1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B2">
+      <c r="B6">
+        <v>70</v>
+      </c>
+      <c r="C6">
+        <v>0.95</v>
+      </c>
+      <c r="D6">
+        <v>0.08</v>
+      </c>
+      <c r="E6">
+        <v>1.7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>80</v>
+      </c>
+      <c r="C7">
+        <v>0.8</v>
+      </c>
+      <c r="D7">
+        <v>0.05</v>
+      </c>
+      <c r="E7">
+        <v>2.1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>110</v>
+      </c>
+      <c r="C8">
+        <v>0.8</v>
+      </c>
+      <c r="D8">
+        <v>0.15</v>
+      </c>
+      <c r="E8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>115</v>
+      </c>
+      <c r="C9">
+        <v>0.75</v>
+      </c>
+      <c r="D9">
+        <v>0.05</v>
+      </c>
+      <c r="E9">
+        <v>2.5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>95</v>
+      </c>
+      <c r="C10">
+        <v>1.2</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+      <c r="E10">
+        <v>1.5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>140</v>
+      </c>
+      <c r="C11">
+        <v>0.7</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
+        <v>2.8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0.05</v>
+      </c>
+      <c r="E12">
+        <v>1.5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>38</v>
+      </c>
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0.5</v>
-      </c>
-      <c r="E2">
+      <c r="D13">
+        <v>0.05</v>
+      </c>
+      <c r="E13">
+        <v>1.5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>45</v>
+      </c>
+      <c r="C14">
+        <v>0.9</v>
+      </c>
+      <c r="D14">
+        <v>0.05</v>
+      </c>
+      <c r="E14">
+        <v>1.5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>55</v>
+      </c>
+      <c r="C15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F2">
+      <c r="D15">
+        <v>0.1</v>
+      </c>
+      <c r="E15">
+        <v>1.5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16">
+        <v>50</v>
+      </c>
+      <c r="C16">
+        <v>1.2</v>
+      </c>
+      <c r="D16">
+        <v>0.15</v>
+      </c>
+      <c r="E16">
+        <v>1.5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17">
+        <v>58</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="D17">
+        <v>0.08</v>
+      </c>
+      <c r="E17">
+        <v>1.6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>80</v>
+      </c>
+      <c r="C18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D18">
+        <v>0.15</v>
+      </c>
+      <c r="E18">
+        <v>1.8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>85</v>
+      </c>
+      <c r="C19">
+        <v>0.9</v>
+      </c>
+      <c r="D19">
         <v>0.2</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H19" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>1.3</v>
+      </c>
+      <c r="D20">
+        <v>0.1</v>
+      </c>
+      <c r="E20">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21">
+        <v>105</v>
+      </c>
+      <c r="C21">
+        <v>1.2</v>
+      </c>
+      <c r="D21">
+        <v>0.15</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22">
+        <v>75</v>
+      </c>
+      <c r="C22">
+        <v>1.2</v>
+      </c>
+      <c r="D22">
+        <v>0.25</v>
+      </c>
+      <c r="E22">
+        <v>1.8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D23">
+        <v>0.1</v>
+      </c>
+      <c r="E23">
+        <v>1.5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24">
+        <v>35</v>
+      </c>
+      <c r="C24">
+        <v>1.3</v>
+      </c>
+      <c r="D24">
+        <v>0.15</v>
+      </c>
+      <c r="E24">
+        <v>1.5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" t="s">
+        <v>110</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>55</v>
+      </c>
+      <c r="C25">
+        <v>1.4</v>
+      </c>
+      <c r="D25">
+        <v>0.15</v>
+      </c>
+      <c r="E25">
+        <v>1.6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" t="s">
+        <v>112</v>
+      </c>
+      <c r="H25" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" t="s">
+        <v>61</v>
+      </c>
+      <c r="J25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>65</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0.2</v>
+      </c>
+      <c r="E26">
+        <v>1.8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H26" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>85</v>
+      </c>
+      <c r="C27">
+        <v>1.5</v>
+      </c>
+      <c r="D27">
+        <v>0.25</v>
+      </c>
+      <c r="E27">
+        <v>1.7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>0.8</v>
+      </c>
+      <c r="D28">
+        <v>0.2</v>
+      </c>
+      <c r="E28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s">
+        <v>61</v>
+      </c>
+      <c r="J28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>70</v>
+      </c>
+      <c r="C29">
+        <v>1.8</v>
+      </c>
+      <c r="D29">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>1.5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>120</v>
+      </c>
+      <c r="C30">
+        <v>1.2</v>
+      </c>
+      <c r="D30">
+        <v>0.3</v>
+      </c>
+      <c r="E30">
+        <v>2.5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>0.9</v>
+      </c>
+      <c r="D31">
+        <v>0.05</v>
+      </c>
+      <c r="E31">
+        <v>1.5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" t="s">
+        <v>61</v>
+      </c>
+      <c r="J31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>42</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>0.05</v>
+      </c>
+      <c r="E32">
+        <v>1.5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>61</v>
+      </c>
+      <c r="J32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
+        <v>65</v>
+      </c>
+      <c r="C33">
+        <v>0.9</v>
+      </c>
+      <c r="D33">
+        <v>0.1</v>
+      </c>
+      <c r="E33">
+        <v>1.6</v>
+      </c>
+      <c r="F33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" t="s">
+        <v>61</v>
+      </c>
+      <c r="J33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34">
+        <v>60</v>
+      </c>
+      <c r="C34">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D34">
+        <v>0.08</v>
+      </c>
+      <c r="E34">
+        <v>1.5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H34" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <v>55</v>
+      </c>
+      <c r="C35">
+        <v>1.2</v>
+      </c>
+      <c r="D35">
+        <v>0.1</v>
+      </c>
+      <c r="E35">
+        <v>1.5</v>
+      </c>
+      <c r="F35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35" t="s">
+        <v>67</v>
+      </c>
+      <c r="I35" t="s">
+        <v>61</v>
+      </c>
+      <c r="J35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36">
+        <v>95</v>
+      </c>
+      <c r="C36">
+        <v>0.9</v>
+      </c>
+      <c r="D36">
+        <v>0.15</v>
+      </c>
+      <c r="E36">
+        <v>1.8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H36" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" t="s">
+        <v>61</v>
+      </c>
+      <c r="J36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>90</v>
+      </c>
+      <c r="C37">
+        <v>0.85</v>
+      </c>
+      <c r="D37">
+        <v>0.1</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38">
+        <v>80</v>
+      </c>
+      <c r="C38">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D38">
+        <v>0.2</v>
+      </c>
+      <c r="E38">
+        <v>1.5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>0.05</v>
+      </c>
+      <c r="E39">
+        <v>1.5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>61</v>
+      </c>
+      <c r="J39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40">
+        <v>48</v>
+      </c>
+      <c r="C40">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D40">
+        <v>0.08</v>
+      </c>
+      <c r="E40">
+        <v>1.5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>61</v>
+      </c>
+      <c r="J40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
+        <v>65</v>
+      </c>
+      <c r="C41">
+        <v>1.2</v>
+      </c>
+      <c r="D41">
+        <v>0.15</v>
+      </c>
+      <c r="E41">
+        <v>1.6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" t="s">
+        <v>144</v>
+      </c>
+      <c r="H41" t="s">
+        <v>67</v>
+      </c>
+      <c r="I41" t="s">
+        <v>61</v>
+      </c>
+      <c r="J41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42">
+        <v>70</v>
+      </c>
+      <c r="C42">
+        <v>1.05</v>
+      </c>
+      <c r="D42">
+        <v>0.1</v>
+      </c>
+      <c r="E42">
+        <v>1.7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" t="s">
+        <v>67</v>
+      </c>
+      <c r="I42" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43">
+        <v>95</v>
+      </c>
+      <c r="C43">
+        <v>1.2</v>
+      </c>
+      <c r="D43">
+        <v>0.15</v>
+      </c>
+      <c r="E43">
+        <v>1.8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s">
+        <v>61</v>
+      </c>
+      <c r="J43" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44">
+        <v>105</v>
+      </c>
+      <c r="C44">
+        <v>0.9</v>
+      </c>
+      <c r="D44">
+        <v>0.1</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>149</v>
+      </c>
+      <c r="G44" t="s">
+        <v>150</v>
+      </c>
+      <c r="H44" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45">
+        <v>85</v>
+      </c>
+      <c r="C45">
+        <v>1.3</v>
+      </c>
+      <c r="D45">
+        <v>0.15</v>
+      </c>
+      <c r="E45">
+        <v>1.5</v>
+      </c>
+      <c r="F45" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46">
+        <v>130</v>
+      </c>
+      <c r="C46">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D46">
+        <v>0.2</v>
+      </c>
+      <c r="E46">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F46" t="s">
+        <v>153</v>
+      </c>
+      <c r="G46" t="s">
+        <v>154</v>
+      </c>
+      <c r="H46" t="s">
+        <v>85</v>
+      </c>
+      <c r="I46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="B2:B1048576">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="B23:B1048576 B2:B21">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G2:G1048576">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="단위 확인 (Cooldown)" error="쿨타임은 0보다 작을 수 없습니다._x000a__x000a_※ 단위: 초 (Seconds)_x000a_- 1분 = '60' 입력_x000a_- 0.5초 = '0.5' 입력_x000a_- 쿨타임 없음 = '0' 입력_x000a__x000a_밀리초(ms) 단위가 아닙니다! 다시 확인해주세요." sqref="G23:G1048576 G2:G21">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="확률은 0.0 ~ 1.0 사이의 소수점만 가능합니다. (예: 15% -&gt; 0.15)" sqref="D2:D1048576">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="확률은 0.0 ~ 1.0 사이의 소수점만 가능합니다. (예: 15% -&gt; 0.15)" sqref="D23:D1048576 D2:D21">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="CritDamage(치명타 배율)는 최소 1.0 이상이어야 합니다." sqref="E2:E1048576">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="CritDamage(치명타 배율)는 최소 1.0 이상이어야 합니다." sqref="E23:E1048576 E2:E21">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="C2:C1048576">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="입력 오류" error="음수(-)는 입력할 수 없습니다. 0 이상의 숫자를 입력해주세요." sqref="C23:C1048576 C2:C21">
       <formula1>0.1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="사거리는 0보다 작을 수 없습니다._x000a__x000a_※ 중요: 언리얼 단위(cm) 기준입니다!_x000a_(미터법 입력 금지)_x000a__x000a_[올바른 예시]_x000a_- 1m 사거리 = '100' 입력_x000a_- 1.5m 사거리 = '150' 입력_x000a_- 5m 사거리 = '500' 입력_x000a__x000a_'1.5'라고 적으면 1.5cm가 됩니다! 다시 확인해주세요." sqref="F2:F1048576">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="범위 오류" error="사거리는 0보다 작을 수 없습니다._x000a__x000a_※ 중요: 언리얼 단위(cm) 기준입니다!_x000a_(미터법 입력 금지)_x000a__x000a_[올바른 예시]_x000a_- 1m 사거리 = '100' 입력_x000a_- 1.5m 사거리 = '150' 입력_x000a_- 5m 사거리 = '500' 입력_x000a__x000a_'1.5'라고 적으면 1.5cm가 됩니다! 다시 확인해주세요." sqref="F23:F1048576 F2:F21">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="글자 수 초과 (DisplayName)" error="아이템 이름이 너무 깁니다! (최대 20자)_x000a__x000a_UI 텍스트 박스를 넘어갈 위험이 있습니다._x000a_더 짧게 줄이거나, 줄바꿈이 필요한지 확인해주세요." sqref="H2:H1048576">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="글자 수 초과 (DisplayName)" error="아이템 이름이 너무 깁니다! (최대 20자)_x000a__x000a_UI 텍스트 박스를 넘어갈 위험이 있습니다._x000a_더 짧게 줄이거나, 줄바꿈이 필요한지 확인해주세요." sqref="H23:H1048576 H2:H21">
       <formula1>20</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="설명 길이 확인" error="설명이 너무 깁니다. (100자 제한)_x000a__x000a_※ 팁:_x000a_줄바꿈이 필요하면 [Alt + Enter]를 사용하세요._x000a_너무 긴 설명은 툴팁 가독성을 해칩니다." sqref="I2:I1048576">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="설명 길이 확인" error="설명이 너무 깁니다. (100자 제한)_x000a__x000a_※ 팁:_x000a_줄바꿈이 필요하면 [Alt + Enter]를 사용하세요._x000a_너무 긴 설명은 툴팁 가독성을 해칩니다." sqref="I23:I1048576 I2:I21">
       <formula1>100</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)_x000a__x000a_다른 이름을 입력해주세요." sqref="A1:A1048576">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)_x000a__x000a_다른 이름을 입력해주세요." sqref="A1:A21 A23:A1048576">
       <formula1>COUNTIF($A:$A, A1) &lt;= 1</formula1>
     </dataValidation>
   </dataValidations>
@@ -1134,7 +2944,7 @@
           <x14:formula1>
             <xm:f>Rarity!$A$1:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
+          <xm:sqref>J23:J1048576 J2:J21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1149,27 +2959,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/DesignData/Excel_Masters/WeaponStats_Master.xlsx
+++ b/DesignData/Excel_Masters/WeaponStats_Master.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25680" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="WeaponStats" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="233">
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>SetID</t>
+  </si>
+  <si>
+    <t>LevelUpCostId</t>
+  </si>
+  <si>
     <t>AttackPower</t>
   </si>
   <si>
@@ -36,457 +51,673 @@
     <t>CritDamage</t>
   </si>
   <si>
-    <t>DisplayName</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Rarity</t>
-  </si>
-  <si>
-    <t>SetID</t>
-  </si>
-  <si>
-    <t>LevelUpCostId</t>
+    <t>BasicAttackActionID</t>
+  </si>
+  <si>
+    <t>SkillActionID</t>
   </si>
   <si>
     <t>Blunt_DefaultBlunt</t>
   </si>
   <si>
+    <t>湲곕낯 ?붽린</t>
+  </si>
+  <si>
+    <t>?명븯寃??????덈뒗 ?섎Т 紐쎈뫁?댁엯?덈떎.</t>
+  </si>
+  <si>
     <t>Common</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
+    <t>Cost_Common</t>
+  </si>
+  <si>
+    <t>W_Blunt_DefaultBlunt_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_DefaultBlunt_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Wrench</t>
   </si>
   <si>
+    <t>?뚯튂</t>
+  </si>
+  <si>
+    <t>怨듦뎄?⑥뿉??爰쇰궦 臾듭쭅???뚯튂?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Blunt_Wrench_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Wrench_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Cleaner</t>
   </si>
   <si>
+    <t>泥?냼遺??鍮쀬옄猷?癒쇱? ????곸쓣 ?몄뼱踰꾨━??鍮쀬옄猷⑥엯?덈떎.</t>
+  </si>
+  <si>
     <t>Rare</t>
   </si>
   <si>
     <t>Cost_Rare</t>
   </si>
   <si>
+    <t>W_Blunt_Cleaner_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Cleaner_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Nobel</t>
   </si>
   <si>
+    <t>?몃꺼??留앹튂</t>
+  </si>
+  <si>
+    <t>?붿빟 ?꾩깉媛 ?섎뒗 ?꾪뿕??留앹튂?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Blunt_Nobel_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Nobel_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Nurse</t>
   </si>
   <si>
+    <t>媛꾪샇?ъ쓽 二쇱궗湲?嫄곕???二쇱궗湲??뺥깭??臾닿린?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Blunt_Nurse_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Nurse_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Tuner</t>
   </si>
   <si>
+    <t>議곗쑉?먯쓽 ?대㉧</t>
+  </si>
+  <si>
+    <t>遺덊삊?붿쓬??遺?섎뒗 嫄곕????대㉧?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Blunt_Tuner_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Tuner_Skl</t>
+  </si>
+  <si>
     <t>Blunt_DevilBat</t>
   </si>
   <si>
+    <t>?낅쭏??諛⑸쭩???낅쭏??湲곗슫??源껊뱺 媛??諛뺥엺 諛고듃?낅땲??</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
     <t>Cost_Epic</t>
   </si>
   <si>
+    <t>W_Blunt_DevilBat_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_DevilBat_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Outsider</t>
   </si>
   <si>
+    <t>?대갑?몄쓽 怨↔눌???????녿뒗 ?ъ쭏濡?留뚮뱾?댁쭊 臾닿굅??怨↔눌?댁엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Blunt_Outsider_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Outsider_Skl</t>
+  </si>
+  <si>
     <t>Blunt_Event_01</t>
   </si>
   <si>
+    <t>?⑷툑 肉낅쭩移?(?대깽??</t>
+  </si>
+  <si>
+    <t>留욎쑝硫?湲곕텇??臾섑븯寃??곹븯??肉낅쭩移섏엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Blunt_Event_01_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_Event_01_Skl</t>
+  </si>
+  <si>
     <t>Blunt_TreasureChest</t>
   </si>
   <si>
+    <t>蹂대Ъ?곸옄 泥좏눜</t>
+  </si>
+  <si>
+    <t>湲덊솕媛 ?잛븘???섏삱 寃?媛숈? 泥좏눜?낅땲??</t>
+  </si>
+  <si>
     <t>Legendary</t>
   </si>
   <si>
+    <t>Cost_Legendary</t>
+  </si>
+  <si>
+    <t>W_Blunt_TreasureChest_Atk</t>
+  </si>
+  <si>
+    <t>W_Blunt_TreasureChest_Skl</t>
+  </si>
+  <si>
     <t>Book_DefaultBook</t>
   </si>
   <si>
+    <t>湲곕낯 留덈룄??留덈쾿??湲곗큹媛 ?곹??덈뒗 ?≪? 梨낆엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Book_DefaultBook_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_DefaultBook_Skl</t>
+  </si>
+  <si>
     <t>Book_CookingForDummies</t>
   </si>
   <si>
+    <t>?붾━ 湲곗큹 梨?留덈쾿???곌린 醫뗭? ?덉떆?쇰턿?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Book_CookingForDummies_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_CookingForDummies_Skl</t>
+  </si>
+  <si>
     <t>Book_Dictionary</t>
   </si>
   <si>
+    <t>?먭볼???ъ쟾</t>
+  </si>
+  <si>
+    <t>臾쇰━?곸쑝濡??뚮젮???꾪뵆 寃?媛숈? ?ъ쟾?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Book_Dictionary_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_Dictionary_Skl</t>
+  </si>
+  <si>
     <t>Book_DeckCase</t>
   </si>
   <si>
+    <t>??耳?댁뒪</t>
+  </si>
+  <si>
+    <t>留덈쾿 移대뱶媛 媛???ㅼ뼱?덈뒗 耳?댁뒪?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Book_DeckCase_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_DeckCase_Skl</t>
+  </si>
+  <si>
     <t>Book_HologramHud</t>
   </si>
   <si>
+    <t>?濡쒓렇??HUD</t>
+  </si>
+  <si>
+    <t>泥⑤떒 湲곗닠??吏묒빟泥??뺣낫 ?ъ쁺湲곗엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Book_HologramHud_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_HologramHud_Skl</t>
+  </si>
+  <si>
     <t>Book_PerfectHarmony</t>
   </si>
   <si>
+    <t>?꾨꼍??議고솕</t>
+  </si>
+  <si>
+    <t>?먯뿰???댁튂媛 ?닿릿 ?좊퉬??梨낆엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Book_PerfectHarmony_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_PerfectHarmony_Skl</t>
+  </si>
+  <si>
     <t>Book_BookOfRed</t>
   </si>
   <si>
+    <t>遺됱? 梨??뤿튆 留덈젰???먮Ⅴ??留덈룄?쒖엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Book_BookOfRed_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_BookOfRed_Skl</t>
+  </si>
+  <si>
     <t>Book_MementoMori</t>
   </si>
   <si>
+    <t>硫붾찘??紐⑤━</t>
+  </si>
+  <si>
+    <t>二쎌쓬??湲곗뼲?섍쾶 留뚮뱶??遺덇만???쒖쟻?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Book_MementoMori_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_MementoMori_Skl</t>
+  </si>
+  <si>
     <t>Book_Event_01</t>
   </si>
   <si>
+    <t>異뺤젣??留덈룄??(?대깽??</t>
+  </si>
+  <si>
+    <t>??＝ 留덈쾿??臾댄븳???잛븘吏묐땲??</t>
+  </si>
+  <si>
+    <t>W_Book_Event_01_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_Event_01_Skl</t>
+  </si>
+  <si>
     <t>Book_FlawlessPlaying</t>
   </si>
   <si>
+    <t>?꾨꼍???곗＜</t>
+  </si>
+  <si>
+    <t>?멸퀎瑜??곗＜?????덈뒗 ?좊퉬?곸씤 ?낅낫?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Book_FlawlessPlaying_Atk</t>
+  </si>
+  <si>
+    <t>W_Book_FlawlessPlaying_Skl</t>
+  </si>
+  <si>
     <t>Gun_BlackNose</t>
   </si>
   <si>
+    <t>釉붾옓 ?몄쫰</t>
+  </si>
+  <si>
+    <t>?붿빟 ?꾩깉媛 吏숆쾶 諛?沅뚯킑?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Gun_BlackNose_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_BlackNose_Skl</t>
+  </si>
+  <si>
     <t>Gun_Smithers</t>
   </si>
   <si>
+    <t>寃쎈퉬蹂묒쓽 珥??됰쾾??寃쎈퉬蹂묐뱾???ъ슜?섎뒗 珥앹엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Gun_Smithers_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_Smithers_Skl</t>
+  </si>
+  <si>
     <t>Gun_Nail_Gun</t>
   </si>
   <si>
+    <t>?ㅼ씪 嫄?怨듭궗?μ뿉???곕뜕 紐?諛뺣뒗 湲곌퀎?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Gun_Nail_Gun_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_Nail_Gun_Skl</t>
+  </si>
+  <si>
     <t>Gun_LovelyCoil</t>
   </si>
   <si>
+    <t>?щ툝由?肄붿씪</t>
+  </si>
+  <si>
+    <t>洹?ъ슫 ?명삎怨??щ━ ?댁긽?μ씠 ?믪뒿?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Gun_LovelyCoil_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_LovelyCoil_Skl</t>
+  </si>
+  <si>
     <t>Gun_Mustang</t>
   </si>
   <si>
+    <t>癒몄뒪??諛섎룞? 嫄곗튌吏留??뚭눼?곸씤 沅뚯킑?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Gun_Mustang_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_Mustang_Skl</t>
+  </si>
+  <si>
     <t>Gun_PayBack</t>
   </si>
   <si>
+    <t>?섏씠諛?諛쏆? 留뚰겮 ?뚮젮二쇰뒗 蹂듭닔珥앹엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Gun_PayBack_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_PayBack_Skl</t>
+  </si>
+  <si>
     <t>Gun_Demonia</t>
   </si>
   <si>
+    <t>?곕え?덉븘</t>
+  </si>
+  <si>
+    <t>留덇퀎??湲덉냽?쇰줈 踰쇰젮???룰굔?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Gun_Demonia_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_Demonia_Skl</t>
+  </si>
+  <si>
     <t>Gun_Event_01</t>
   </si>
   <si>
+    <t>臾쇱킑 (?대깽??</t>
+  </si>
+  <si>
+    <t>?앷컖蹂대떎 ?섏븬??媛뺥븳 ?λ궃媛?臾쇱킑?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Gun_Event_01_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_Event_01_Skl</t>
+  </si>
+  <si>
     <t>Gun_BlackBeard</t>
   </si>
   <si>
+    <t>寃? ?섏뿼</t>
+  </si>
+  <si>
+    <t>?꾩꽕?곸씤 ?댁쟻???ъ슜?섎뜕 ?묒깋 ?붿듅珥앹엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Gun_BlackBeard_Atk</t>
+  </si>
+  <si>
+    <t>W_Gun_BlackBeard_Skl</t>
+  </si>
+  <si>
     <t>Staff_Rogue</t>
   </si>
   <si>
+    <t>遺덈웾諛곗쓽 留됰?湲?湲멸굅由ъ뿉???뷀엳 以띾뒗 湲?留됰?湲곗엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Staff_Rogue_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_Rogue_Skl</t>
+  </si>
+  <si>
     <t>Staff_Bard</t>
   </si>
   <si>
+    <t>?좊옉?쒖씤??吏?≪씠</t>
+  </si>
+  <si>
+    <t>諛붾엺 ?뚮━媛 ?섎뒗 媛踰쇱슫 吏?≪씠?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_Bard_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_Bard_Skl</t>
+  </si>
+  <si>
     <t>Staff_OneStroke</t>
   </si>
   <si>
+    <t>?쇳븘?섏?</t>
+  </si>
+  <si>
+    <t>?덇났??癒밸Ъ???⑸퓣由щ뒗 嫄곕???遺볦엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Staff_OneStroke_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_OneStroke_Skl</t>
+  </si>
+  <si>
     <t>Staff_Decanter</t>
   </si>
   <si>
+    <t>?붿틪??吏?≪씠</t>
+  </si>
+  <si>
+    <t>?щ룄二쇨? ?딆엫?놁씠 ?먮Ⅴ??吏?≪씠?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_Decanter_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_Decanter_Skl</t>
+  </si>
+  <si>
     <t>Staff_Merry</t>
   </si>
   <si>
+    <t>硫붾━ ?ㅽ깭??利먭굅??湲곗슫??肉쒖뼱?대뒗 ?묒썝??吏?≪씠?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_Merry_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_Merry_Skl</t>
+  </si>
+  <si>
     <t>Staff_DeathMatch</t>
   </si>
   <si>
+    <t>?곗뒪留ㅼ튂</t>
+  </si>
+  <si>
+    <t>?쇰? 癒멸툑? ?꾪닾??留덈쾿 吏?≪씠?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_DeathMatch_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_DeathMatch_Skl</t>
+  </si>
+  <si>
     <t>Staff_WinterCane</t>
   </si>
   <si>
+    <t>寃⑥슱??吏?≪씠</t>
+  </si>
+  <si>
+    <t>二쇰????쇱뼱遺숆쾶 留뚮뱶???뱁븳??吏?≪씠?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_WinterCane_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_WinterCane_Skl</t>
+  </si>
+  <si>
     <t>Staff_Event_01</t>
   </si>
   <si>
+    <t>?붿닠 吏?≪씠 (?대깽??</t>
+  </si>
+  <si>
+    <t>?ъ슜???뚮쭏???쒕걚?ъ슫 ?뚮━媛 ?⑸땲??</t>
+  </si>
+  <si>
+    <t>W_Staff_Event_01_Atk</t>
+  </si>
+  <si>
+    <t>W_Staff_Event_01_Skl</t>
+  </si>
+  <si>
     <t>Sword_Army</t>
   </si>
   <si>
+    <t>蹂닿툒??援곗슜寃</t>
+  </si>
+  <si>
+    <t>援곕??먯꽌 ????앹궛?섎뒗 ?쒖? 寃?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_Army_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_Army_Skl</t>
+  </si>
+  <si>
     <t>Sword_ButterSlayer</t>
   </si>
   <si>
+    <t>踰꾪꽣 ?щ젅?댁뼱</t>
+  </si>
+  <si>
+    <t>踰꾪꽣泥섎읆 ?곸쓣 遺?쒕읇寃?踰좎뼱?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_ButterSlayer_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_ButterSlayer_Skl</t>
+  </si>
+  <si>
     <t>Sword_Carver</t>
   </si>
   <si>
+    <t>議곌컖媛??寃</t>
+  </si>
+  <si>
+    <t>?뺣????寃⑹씠 媛?ν븳 ?덈━??議곌컖?꾩엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Sword_Carver_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_Carver_Skl</t>
+  </si>
+  <si>
     <t>Sword_Maid</t>
   </si>
   <si>
+    <t>硫붿씠?쒖쓽 ?κ?</t>
+  </si>
+  <si>
+    <t>泥?냼? ?몄떊 紐⑤몢 ?ν븳 硫붿씠?쒖쓽 寃?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_Maid_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_Maid_Skl</t>
+  </si>
+  <si>
     <t>Sword_BeamSword</t>
   </si>
   <si>
+    <t>鍮??뚮뱶</t>
+  </si>
+  <si>
+    <t>怨좎뿴???뚮씪利덈쭏濡??대（?댁쭊 寃?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_BeamSword_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_BeamSword_Skl</t>
+  </si>
+  <si>
     <t>Sword_ChainSword</t>
   </si>
   <si>
+    <t>泥댁씤 ?뚮뱶</t>
+  </si>
+  <si>
+    <t>?깅땲諛뷀닿? ?뚯븘媛硫??댁젏??李?뼱?낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_ChainSword_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_ChainSword_Skl</t>
+  </si>
+  <si>
     <t>Sword_Event_01</t>
   </si>
   <si>
+    <t>愿묒꽑寃 (?대깽??</t>
+  </si>
+  <si>
+    <t>?숈쐷嫄곕━???뚮━媛 留ㅻ젰?곸씤 ?λ궃媛먯엯?덈떎.</t>
+  </si>
+  <si>
+    <t>W_Sword_Event_01_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_Event_01_Skl</t>
+  </si>
+  <si>
     <t>Sword_MilkyWay</t>
   </si>
   <si>
-    <t>BasicAttackActionID</t>
-  </si>
-  <si>
-    <t>SkillActionID</t>
-  </si>
-  <si>
-    <t>기본 둔기</t>
-  </si>
-  <si>
-    <t>흔하게 볼 수 있는 나무 몽둥이입니다.</t>
-  </si>
-  <si>
-    <t>Cost_Common</t>
-  </si>
-  <si>
-    <t>렌치</t>
-  </si>
-  <si>
-    <t>공구함에서 꺼낸 묵직한 렌치입니다.</t>
-  </si>
-  <si>
-    <t>청소부의 빗자루</t>
-  </si>
-  <si>
-    <t>먼지 대신 적을 쓸어버리는 빗자루입니다.</t>
-  </si>
-  <si>
-    <t>노벨의 망치</t>
-  </si>
-  <si>
-    <t>화약 냄새가 나는 위험한 망치입니다.</t>
-  </si>
-  <si>
-    <t>간호사의 주사기</t>
-  </si>
-  <si>
-    <t>거대한 주사기 형태의 둔기입니다.</t>
-  </si>
-  <si>
-    <t>조율자의 해머</t>
-  </si>
-  <si>
-    <t>불협화음을 부수는 거대한 해머입니다.</t>
-  </si>
-  <si>
-    <t>악마의 방망이</t>
-  </si>
-  <si>
-    <t>악마의 기운이 깃든 가시 박힌 배트입니다.</t>
-  </si>
-  <si>
-    <t>이방인의 곡괭이</t>
-  </si>
-  <si>
-    <t>알 수 없는 재질로 만들어진 무거운 곡괭이입니다.</t>
-  </si>
-  <si>
-    <t>황금 뿅망치 (이벤트)</t>
-  </si>
-  <si>
-    <t>맞으면 기분이 묘하게 상쾌한 뿅망치입니다.</t>
-  </si>
-  <si>
-    <t>보물상자 철퇴</t>
-  </si>
-  <si>
-    <t>금화가 쏟아져 나올 것 같은 철퇴입니다.</t>
-  </si>
-  <si>
-    <t>Cost_Legendary</t>
-  </si>
-  <si>
-    <t>기본 마도서</t>
-  </si>
-  <si>
-    <t>마법의 기초가 적혀있는 낡은 책입니다.</t>
-  </si>
-  <si>
-    <t>요리 기초 책</t>
-  </si>
-  <si>
-    <t>마법에 쓰기 좋은 레시피북입니다.</t>
-  </si>
-  <si>
-    <t>두꺼운 사전</t>
-  </si>
-  <si>
-    <t>물리적으로 때려도 아플 것 같은 사전입니다.</t>
-  </si>
-  <si>
-    <t>덱 케이스</t>
-  </si>
-  <si>
-    <t>마법 카드가 가득 들어있는 케이스입니다.</t>
-  </si>
-  <si>
-    <t>홀로그램 HUD</t>
-  </si>
-  <si>
-    <t>첨단 기술의 집약체 정보 투영기입니다.</t>
-  </si>
-  <si>
-    <t>완벽한 조화</t>
-  </si>
-  <si>
-    <t>자연의 이치가 담긴 신비한 책입니다.</t>
-  </si>
-  <si>
-    <t>붉은 책</t>
-  </si>
-  <si>
-    <t>핏빛 마력이 흐르는 마도서입니다.</t>
-  </si>
-  <si>
-    <t>메멘토 모리</t>
-  </si>
-  <si>
-    <t>죽음을 기억하게 만드는 불길한 서적입니다.</t>
-  </si>
-  <si>
-    <t>축제의 마도서 (이벤트)</t>
-  </si>
-  <si>
-    <t>폭죽 마법이 무한히 쏟아집니다.</t>
-  </si>
-  <si>
-    <t>완벽한 연주</t>
-  </si>
-  <si>
-    <t>세계를 연주할 수 있는 신비적인 악보입니다.</t>
-  </si>
-  <si>
-    <t>블랙 노즈</t>
-  </si>
-  <si>
-    <t>화약 냄새가 짙게 밴 권총입니다.</t>
-  </si>
-  <si>
-    <t>경비병의 총</t>
-  </si>
-  <si>
-    <t>평범한 경비병들이 사용하는 총입니다.</t>
-  </si>
-  <si>
-    <t>네일 건</t>
-  </si>
-  <si>
-    <t>공사장에서 쓰던 못 박는 기계입니다.</t>
-  </si>
-  <si>
-    <t>러블리 코일</t>
-  </si>
-  <si>
-    <t>귀여운 외형과 달리 살상력이 높습니다.</t>
-  </si>
-  <si>
-    <t>머스탱</t>
-  </si>
-  <si>
-    <t>반동이 거칠지만 위력적인 권총입니다.</t>
-  </si>
-  <si>
-    <t>페이백</t>
-  </si>
-  <si>
-    <t>받은 만큼 돌려주는 복수총입니다.</t>
-  </si>
-  <si>
-    <t>데모니아</t>
-  </si>
-  <si>
-    <t>마계의 금속으로 벼려낸 산탄총입니다.</t>
-  </si>
-  <si>
-    <t>물총 (이벤트)</t>
-  </si>
-  <si>
-    <t>생각보다 수압이 강한 장난감 물총입니다.</t>
-  </si>
-  <si>
-    <t>검은 수염</t>
-  </si>
-  <si>
-    <t>전설적인 해적이 사용하던 쌍열 화승총입니다.</t>
-  </si>
-  <si>
-    <t>불량배의 막대기</t>
-  </si>
-  <si>
-    <t>길거리에서 흔히 줍는 긴 막대기입니다.</t>
-  </si>
-  <si>
-    <t>유랑시인의 지팡이</t>
-  </si>
-  <si>
-    <t>바람 소리가 나는 가벼운 지팡이입니다.</t>
-  </si>
-  <si>
-    <t>일필휘지</t>
-  </si>
-  <si>
-    <t>허공에 먹물을 흩뿌리는 거대한 붓입니다.</t>
-  </si>
-  <si>
-    <t>디캔터 지팡이</t>
-  </si>
-  <si>
-    <t>포도주가 끊임없이 흐르는 지팡이입니다.</t>
-  </si>
-  <si>
-    <t>메리 스태프</t>
-  </si>
-  <si>
-    <t>즐거운 기운을 뿜어내는 응원용 지팡이입니다.</t>
-  </si>
-  <si>
-    <t>데스매치</t>
-  </si>
-  <si>
-    <t>피를 머금은 전투용 마법 지팡이입니다.</t>
-  </si>
-  <si>
-    <t>겨울의 지팡이</t>
-  </si>
-  <si>
-    <t>주변을 얼어붙게 만드는 혹한의 지팡이입니다.</t>
-  </si>
-  <si>
-    <t>폭죽 지팡이 (이벤트)</t>
-  </si>
-  <si>
-    <t>사용할 때마다 시끄러운 소리가 납니다.</t>
-  </si>
-  <si>
-    <t>보급형 군용검</t>
-  </si>
-  <si>
-    <t>군대에서 대량 생산하는 표준 검입니다.</t>
-  </si>
-  <si>
-    <t>버터 슬레이어</t>
-  </si>
-  <si>
-    <t>버터처럼 적을 부드럽게 베어냅니다.</t>
-  </si>
-  <si>
-    <t>조각가의 검</t>
-  </si>
-  <si>
-    <t>정밀한 타격이 가능한 예리한 조각도입니다.</t>
-  </si>
-  <si>
-    <t>메이드의 장검</t>
-  </si>
-  <si>
-    <t>청소와 암살 모두 능한 메이드의 검입니다.</t>
-  </si>
-  <si>
-    <t>빔 소드</t>
-  </si>
-  <si>
-    <t>고열의 플라즈마로 이루어진 검입니다.</t>
-  </si>
-  <si>
-    <t>체인 소드</t>
-  </si>
-  <si>
-    <t>톱니바퀴가 돌아가며 살점을 찢어냅니다.</t>
-  </si>
-  <si>
-    <t>광선검 (이벤트)</t>
-  </si>
-  <si>
-    <t>웅웅거리는 소리가 매력적인 장난감입니다.</t>
-  </si>
-  <si>
-    <t>은하수 검</t>
-  </si>
-  <si>
-    <t>휘두를 때마다 별빛이 쏟아지는 성검입니다.</t>
+    <t>??섏닔 寃</t>
+  </si>
+  <si>
+    <t>?섎몢瑜??뚮쭏??蹂꾨튆???잛븘吏???깃??낅땲??</t>
+  </si>
+  <si>
+    <t>W_Sword_MilkyWay_Atk</t>
+  </si>
+  <si>
+    <t>W_Sword_MilkyWay_Skl</t>
   </si>
 </sst>
 </file>
@@ -1412,57 +1643,57 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>4</v>
-      </c>
       <c r="K1" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G2">
         <v>55</v>
@@ -1477,30 +1708,30 @@
         <v>1.5</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -1515,68 +1746,65 @@
         <v>1.6</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>75</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
-      </c>
-      <c r="J4">
         <v>1.8</v>
       </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
       <c r="K4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>85</v>
@@ -1591,68 +1819,65 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="F6">
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>70</v>
+        <v>0.95</v>
       </c>
       <c r="H6">
-        <v>0.95</v>
+        <v>0.08</v>
       </c>
       <c r="I6">
-        <v>0.08</v>
-      </c>
-      <c r="J6">
         <v>1.7</v>
       </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
       <c r="K6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>80</v>
@@ -1667,106 +1892,100 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>110</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>0.8</v>
       </c>
       <c r="H8">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="I8">
-        <v>0.15</v>
-      </c>
-      <c r="J8">
         <v>2.2000000000000002</v>
       </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
       <c r="K8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
+        <v>48</v>
+      </c>
+      <c r="F9">
+        <v>115</v>
       </c>
       <c r="G9">
-        <v>115</v>
+        <v>0.75</v>
       </c>
       <c r="H9">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
       <c r="I9">
-        <v>0.05</v>
-      </c>
-      <c r="J9">
         <v>2.5</v>
       </c>
+      <c r="J9" t="s">
+        <v>53</v>
+      </c>
       <c r="K9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>95</v>
@@ -1781,30 +2000,30 @@
         <v>1.5</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>140</v>
@@ -1819,106 +2038,100 @@
         <v>2.8</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F12">
+        <v>35</v>
       </c>
       <c r="G12">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I12">
-        <v>0.05</v>
-      </c>
-      <c r="J12">
         <v>1.5</v>
       </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
       <c r="K12" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <v>38</v>
       </c>
       <c r="G13">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="I13">
-        <v>0.05</v>
-      </c>
-      <c r="J13">
         <v>1.5</v>
       </c>
+      <c r="J13" t="s">
+        <v>73</v>
+      </c>
       <c r="K13" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G14">
         <v>45</v>
@@ -1933,30 +2146,30 @@
         <v>1.5</v>
       </c>
       <c r="K14" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G15">
         <v>55</v>
@@ -1971,30 +2184,30 @@
         <v>1.5</v>
       </c>
       <c r="K15" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G16">
         <v>50</v>
@@ -2009,30 +2222,30 @@
         <v>1.5</v>
       </c>
       <c r="K16" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G17">
         <v>58</v>
@@ -2047,53 +2260,50 @@
         <v>1.6</v>
       </c>
       <c r="K17" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="L17" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H18">
+        <v>0.15</v>
+      </c>
+      <c r="I18">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" t="s">
         <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18">
-        <v>80</v>
-      </c>
-      <c r="H18">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I18">
-        <v>0.15</v>
-      </c>
-      <c r="J18">
-        <v>1.8</v>
-      </c>
-      <c r="K18" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
         <v>100</v>
@@ -2102,13 +2312,13 @@
         <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G19">
         <v>85</v>
@@ -2123,30 +2333,30 @@
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G20">
         <v>75</v>
@@ -2161,30 +2371,30 @@
         <v>1.5</v>
       </c>
       <c r="K20" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G21">
         <v>105</v>
@@ -2199,30 +2409,30 @@
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="L21" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G22">
         <v>75</v>
@@ -2237,106 +2447,100 @@
         <v>1.8</v>
       </c>
       <c r="K22" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="L22" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F23">
+        <v>40</v>
       </c>
       <c r="G23">
-        <v>40</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H23">
-        <v>1.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I23">
-        <v>0.1</v>
-      </c>
-      <c r="J23">
         <v>1.5</v>
       </c>
+      <c r="J23" t="s">
+        <v>121</v>
+      </c>
       <c r="K23" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F24">
+        <v>35</v>
       </c>
       <c r="G24">
-        <v>35</v>
+        <v>1.3</v>
       </c>
       <c r="H24">
-        <v>1.3</v>
+        <v>0.15</v>
       </c>
       <c r="I24">
-        <v>0.15</v>
-      </c>
-      <c r="J24">
         <v>1.5</v>
       </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
       <c r="K24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L24" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G25">
         <v>55</v>
@@ -2351,106 +2555,100 @@
         <v>1.6</v>
       </c>
       <c r="K25" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="F26">
+        <v>65</v>
       </c>
       <c r="G26">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I26">
-        <v>0.2</v>
-      </c>
-      <c r="J26">
         <v>1.8</v>
       </c>
+      <c r="J26" t="s">
+        <v>134</v>
+      </c>
       <c r="K26" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" t="s">
-        <v>22</v>
+        <v>48</v>
+      </c>
+      <c r="F27">
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>85</v>
+        <v>1.5</v>
       </c>
       <c r="H27">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="I27">
-        <v>0.25</v>
-      </c>
-      <c r="J27">
         <v>1.7</v>
       </c>
+      <c r="J27" t="s">
+        <v>138</v>
+      </c>
       <c r="K27" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -2465,30 +2663,30 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="K28" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L28" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G29">
         <v>70</v>
@@ -2503,30 +2701,30 @@
         <v>1.5</v>
       </c>
       <c r="K29" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G30">
         <v>120</v>
@@ -2541,68 +2739,65 @@
         <v>2.5</v>
       </c>
       <c r="K30" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>155</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" t="s">
-        <v>66</v>
+        <v>17</v>
+      </c>
+      <c r="F31">
+        <v>45</v>
       </c>
       <c r="G31">
-        <v>45</v>
+        <v>0.9</v>
       </c>
       <c r="H31">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="I31">
-        <v>0.05</v>
-      </c>
-      <c r="J31">
         <v>1.5</v>
       </c>
+      <c r="J31" t="s">
+        <v>157</v>
+      </c>
       <c r="K31" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G32">
         <v>42</v>
@@ -2617,30 +2812,30 @@
         <v>1.5</v>
       </c>
       <c r="K32" t="s">
-        <v>12</v>
+        <v>162</v>
       </c>
       <c r="L32" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G33">
         <v>65</v>
@@ -2655,30 +2850,30 @@
         <v>1.6</v>
       </c>
       <c r="K33" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
       <c r="L33" t="s">
-        <v>12</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G34">
         <v>60</v>
@@ -2693,68 +2888,65 @@
         <v>1.5</v>
       </c>
       <c r="K34" t="s">
-        <v>12</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="F35">
+        <v>55</v>
       </c>
       <c r="G35">
-        <v>55</v>
+        <v>1.2</v>
       </c>
       <c r="H35">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I35">
-        <v>0.1</v>
-      </c>
-      <c r="J35">
         <v>1.5</v>
       </c>
+      <c r="J35" t="s">
+        <v>176</v>
+      </c>
       <c r="K35" t="s">
-        <v>12</v>
-      </c>
-      <c r="L35" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>178</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G36">
         <v>95</v>
@@ -2769,30 +2961,30 @@
         <v>1.8</v>
       </c>
       <c r="K36" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s">
-        <v>12</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="C37" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G37">
         <v>90</v>
@@ -2807,30 +2999,30 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>12</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G38">
         <v>80</v>
@@ -2845,30 +3037,30 @@
         <v>1.5</v>
       </c>
       <c r="K38" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s">
-        <v>12</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G39">
         <v>50</v>
@@ -2883,30 +3075,30 @@
         <v>1.5</v>
       </c>
       <c r="K39" t="s">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="L39" t="s">
-        <v>12</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G40">
         <v>48</v>
@@ -2921,30 +3113,30 @@
         <v>1.5</v>
       </c>
       <c r="K40" t="s">
-        <v>12</v>
+        <v>201</v>
       </c>
       <c r="L40" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="B41" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G41">
         <v>65</v>
@@ -2959,30 +3151,30 @@
         <v>1.6</v>
       </c>
       <c r="K41" t="s">
-        <v>12</v>
+        <v>206</v>
       </c>
       <c r="L41" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G42">
         <v>70</v>
@@ -2997,30 +3189,30 @@
         <v>1.7</v>
       </c>
       <c r="K42" t="s">
-        <v>12</v>
+        <v>211</v>
       </c>
       <c r="L42" t="s">
-        <v>12</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G43">
         <v>95</v>
@@ -3035,30 +3227,30 @@
         <v>1.8</v>
       </c>
       <c r="K43" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="L43" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G44">
         <v>105</v>
@@ -3073,30 +3265,30 @@
         <v>2</v>
       </c>
       <c r="K44" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="L44" t="s">
-        <v>12</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G45">
         <v>85</v>
@@ -3111,30 +3303,30 @@
         <v>1.5</v>
       </c>
       <c r="K45" t="s">
-        <v>12</v>
+        <v>226</v>
       </c>
       <c r="L45" t="s">
-        <v>12</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G46">
         <v>130</v>
@@ -3149,15 +3341,14 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="K46" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s">
-        <v>12</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>